--- a/single_forces_m-155deg.xlsx
+++ b/single_forces_m-155deg.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E502"/>
+  <dimension ref="A1:C502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,16 +444,6 @@
           <t>Lift</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Drag Mean</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Lift Mean</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,12 +457,6 @@
       <c r="C2" t="n">
         <v>4919.0750228</v>
       </c>
-      <c r="D2" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E2" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -486,12 +470,6 @@
       <c r="C3" t="n">
         <v>4079.90527794</v>
       </c>
-      <c r="D3" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E3" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -505,12 +483,6 @@
       <c r="C4" t="n">
         <v>812.9649909</v>
       </c>
-      <c r="D4" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E4" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -524,12 +496,6 @@
       <c r="C5" t="n">
         <v>-1516.2109615</v>
       </c>
-      <c r="D5" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E5" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -543,12 +509,6 @@
       <c r="C6" t="n">
         <v>-1621.0154213</v>
       </c>
-      <c r="D6" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E6" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -562,12 +522,6 @@
       <c r="C7" t="n">
         <v>-364.8346073</v>
       </c>
-      <c r="D7" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E7" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -581,12 +535,6 @@
       <c r="C8" t="n">
         <v>814.6449142</v>
       </c>
-      <c r="D8" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E8" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -600,12 +548,6 @@
       <c r="C9" t="n">
         <v>1203.16601087</v>
       </c>
-      <c r="D9" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E9" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -619,12 +561,6 @@
       <c r="C10" t="n">
         <v>920.7940059</v>
       </c>
-      <c r="D10" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E10" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -638,12 +574,6 @@
       <c r="C11" t="n">
         <v>469.28078085</v>
       </c>
-      <c r="D11" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E11" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -657,12 +587,6 @@
       <c r="C12" t="n">
         <v>199.71759328</v>
       </c>
-      <c r="D12" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E12" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -676,12 +600,6 @@
       <c r="C13" t="n">
         <v>169.50411141</v>
       </c>
-      <c r="D13" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E13" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -695,12 +613,6 @@
       <c r="C14" t="n">
         <v>256.77258599</v>
       </c>
-      <c r="D14" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E14" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -714,12 +626,6 @@
       <c r="C15" t="n">
         <v>344.5232917</v>
       </c>
-      <c r="D15" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E15" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -733,12 +639,6 @@
       <c r="C16" t="n">
         <v>390.034089</v>
       </c>
-      <c r="D16" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E16" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -752,12 +652,6 @@
       <c r="C17" t="n">
         <v>392.7773495</v>
       </c>
-      <c r="D17" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E17" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -771,12 +665,6 @@
       <c r="C18" t="n">
         <v>361.0567119</v>
       </c>
-      <c r="D18" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E18" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -790,12 +678,6 @@
       <c r="C19" t="n">
         <v>302.5586351</v>
       </c>
-      <c r="D19" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E19" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -809,12 +691,6 @@
       <c r="C20" t="n">
         <v>236.701503</v>
       </c>
-      <c r="D20" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E20" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -828,12 +704,6 @@
       <c r="C21" t="n">
         <v>189.9821509</v>
       </c>
-      <c r="D21" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E21" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -847,12 +717,6 @@
       <c r="C22" t="n">
         <v>176.2977243</v>
       </c>
-      <c r="D22" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E22" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -866,12 +730,6 @@
       <c r="C23" t="n">
         <v>188.6571535</v>
       </c>
-      <c r="D23" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E23" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -885,12 +743,6 @@
       <c r="C24" t="n">
         <v>203.0971099</v>
       </c>
-      <c r="D24" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E24" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -904,12 +756,6 @@
       <c r="C25" t="n">
         <v>203.5983845</v>
       </c>
-      <c r="D25" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E25" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -923,12 +769,6 @@
       <c r="C26" t="n">
         <v>186.4874914</v>
       </c>
-      <c r="D26" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E26" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -942,12 +782,6 @@
       <c r="C27" t="n">
         <v>160.8629596</v>
       </c>
-      <c r="D27" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E27" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -961,12 +795,6 @@
       <c r="C28" t="n">
         <v>138.38033315</v>
       </c>
-      <c r="D28" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E28" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -980,12 +808,6 @@
       <c r="C29" t="n">
         <v>126.791745989</v>
       </c>
-      <c r="D29" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E29" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -999,12 +821,6 @@
       <c r="C30" t="n">
         <v>126.37378428</v>
       </c>
-      <c r="D30" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E30" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1018,12 +834,6 @@
       <c r="C31" t="n">
         <v>129.6727848</v>
       </c>
-      <c r="D31" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E31" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1037,12 +847,6 @@
       <c r="C32" t="n">
         <v>129.6348658</v>
       </c>
-      <c r="D32" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E32" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1056,12 +860,6 @@
       <c r="C33" t="n">
         <v>124.8414485</v>
       </c>
-      <c r="D33" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E33" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1075,12 +873,6 @@
       <c r="C34" t="n">
         <v>118.6658015</v>
       </c>
-      <c r="D34" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E34" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1094,12 +886,6 @@
       <c r="C35" t="n">
         <v>116.0719847</v>
       </c>
-      <c r="D35" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E35" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1113,12 +899,6 @@
       <c r="C36" t="n">
         <v>117.3484021</v>
       </c>
-      <c r="D36" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E36" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1132,12 +912,6 @@
       <c r="C37" t="n">
         <v>120.9111217</v>
       </c>
-      <c r="D37" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E37" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1151,12 +925,6 @@
       <c r="C38" t="n">
         <v>125.2306214</v>
       </c>
-      <c r="D38" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E38" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1170,12 +938,6 @@
       <c r="C39" t="n">
         <v>129.7525577</v>
       </c>
-      <c r="D39" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E39" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1189,12 +951,6 @@
       <c r="C40" t="n">
         <v>134.7900991</v>
       </c>
-      <c r="D40" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E40" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1208,12 +964,6 @@
       <c r="C41" t="n">
         <v>140.6166483</v>
       </c>
-      <c r="D41" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E41" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1227,12 +977,6 @@
       <c r="C42" t="n">
         <v>148.260952</v>
       </c>
-      <c r="D42" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E42" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1246,12 +990,6 @@
       <c r="C43" t="n">
         <v>155.3744423</v>
       </c>
-      <c r="D43" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E43" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1265,12 +1003,6 @@
       <c r="C44" t="n">
         <v>160.8343012</v>
       </c>
-      <c r="D44" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E44" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1284,12 +1016,6 @@
       <c r="C45" t="n">
         <v>165.1710536</v>
       </c>
-      <c r="D45" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E45" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1303,12 +1029,6 @@
       <c r="C46" t="n">
         <v>169.6109014</v>
       </c>
-      <c r="D46" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E46" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1322,12 +1042,6 @@
       <c r="C47" t="n">
         <v>174.5804695</v>
       </c>
-      <c r="D47" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E47" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1341,12 +1055,6 @@
       <c r="C48" t="n">
         <v>179.9780708</v>
       </c>
-      <c r="D48" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E48" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1360,12 +1068,6 @@
       <c r="C49" t="n">
         <v>185.3340928</v>
       </c>
-      <c r="D49" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E49" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1379,12 +1081,6 @@
       <c r="C50" t="n">
         <v>190.4222049</v>
       </c>
-      <c r="D50" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E50" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1398,12 +1094,6 @@
       <c r="C51" t="n">
         <v>195.2927858</v>
       </c>
-      <c r="D51" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E51" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1417,12 +1107,6 @@
       <c r="C52" t="n">
         <v>199.9656374</v>
       </c>
-      <c r="D52" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E52" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1436,12 +1120,6 @@
       <c r="C53" t="n">
         <v>204.4475796</v>
       </c>
-      <c r="D53" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E53" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1455,12 +1133,6 @@
       <c r="C54" t="n">
         <v>208.8198585</v>
       </c>
-      <c r="D54" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E54" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1474,12 +1146,6 @@
       <c r="C55" t="n">
         <v>213.0258057</v>
       </c>
-      <c r="D55" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E55" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1493,12 +1159,6 @@
       <c r="C56" t="n">
         <v>217.0644261</v>
       </c>
-      <c r="D56" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E56" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1512,12 +1172,6 @@
       <c r="C57" t="n">
         <v>220.9396623</v>
       </c>
-      <c r="D57" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E57" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1531,12 +1185,6 @@
       <c r="C58" t="n">
         <v>224.7280566</v>
       </c>
-      <c r="D58" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E58" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1550,12 +1198,6 @@
       <c r="C59" t="n">
         <v>228.3643637</v>
       </c>
-      <c r="D59" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E59" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1569,12 +1211,6 @@
       <c r="C60" t="n">
         <v>231.8510171</v>
       </c>
-      <c r="D60" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E60" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1588,12 +1224,6 @@
       <c r="C61" t="n">
         <v>235.3186441</v>
       </c>
-      <c r="D61" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E61" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1607,12 +1237,6 @@
       <c r="C62" t="n">
         <v>238.6231274</v>
       </c>
-      <c r="D62" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E62" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1626,12 +1250,6 @@
       <c r="C63" t="n">
         <v>241.8992154</v>
       </c>
-      <c r="D63" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E63" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1645,12 +1263,6 @@
       <c r="C64" t="n">
         <v>245.2776094</v>
       </c>
-      <c r="D64" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E64" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1664,12 +1276,6 @@
       <c r="C65" t="n">
         <v>248.5994042</v>
       </c>
-      <c r="D65" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E65" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1683,12 +1289,6 @@
       <c r="C66" t="n">
         <v>251.9133397</v>
       </c>
-      <c r="D66" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E66" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1702,12 +1302,6 @@
       <c r="C67" t="n">
         <v>255.0795869</v>
       </c>
-      <c r="D67" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E67" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1721,12 +1315,6 @@
       <c r="C68" t="n">
         <v>258.3522013</v>
       </c>
-      <c r="D68" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E68" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1740,12 +1328,6 @@
       <c r="C69" t="n">
         <v>261.4305858</v>
       </c>
-      <c r="D69" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E69" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1759,12 +1341,6 @@
       <c r="C70" t="n">
         <v>264.6476058</v>
       </c>
-      <c r="D70" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E70" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1778,12 +1354,6 @@
       <c r="C71" t="n">
         <v>267.8023701</v>
       </c>
-      <c r="D71" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E71" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1797,12 +1367,6 @@
       <c r="C72" t="n">
         <v>270.8939414</v>
       </c>
-      <c r="D72" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E72" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1816,12 +1380,6 @@
       <c r="C73" t="n">
         <v>273.7654841</v>
       </c>
-      <c r="D73" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E73" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1835,12 +1393,6 @@
       <c r="C74" t="n">
         <v>276.9571728</v>
       </c>
-      <c r="D74" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E74" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1854,12 +1406,6 @@
       <c r="C75" t="n">
         <v>279.9477607</v>
       </c>
-      <c r="D75" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E75" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1873,12 +1419,6 @@
       <c r="C76" t="n">
         <v>283.1053498</v>
       </c>
-      <c r="D76" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E76" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1892,12 +1432,6 @@
       <c r="C77" t="n">
         <v>285.8381492</v>
       </c>
-      <c r="D77" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E77" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1911,12 +1445,6 @@
       <c r="C78" t="n">
         <v>288.6521468</v>
       </c>
-      <c r="D78" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E78" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1930,12 +1458,6 @@
       <c r="C79" t="n">
         <v>291.6241059</v>
       </c>
-      <c r="D79" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E79" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1949,12 +1471,6 @@
       <c r="C80" t="n">
         <v>294.6167789</v>
       </c>
-      <c r="D80" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E80" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1968,12 +1484,6 @@
       <c r="C81" t="n">
         <v>297.5803968</v>
       </c>
-      <c r="D81" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E81" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1987,12 +1497,6 @@
       <c r="C82" t="n">
         <v>300.3260717</v>
       </c>
-      <c r="D82" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E82" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2006,12 +1510,6 @@
       <c r="C83" t="n">
         <v>303.0592603</v>
       </c>
-      <c r="D83" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E83" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2025,12 +1523,6 @@
       <c r="C84" t="n">
         <v>305.7078522</v>
       </c>
-      <c r="D84" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E84" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2044,12 +1536,6 @@
       <c r="C85" t="n">
         <v>308.4542845</v>
       </c>
-      <c r="D85" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E85" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2063,12 +1549,6 @@
       <c r="C86" t="n">
         <v>311.1640583</v>
       </c>
-      <c r="D86" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E86" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2082,12 +1562,6 @@
       <c r="C87" t="n">
         <v>313.7730916</v>
       </c>
-      <c r="D87" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E87" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2101,12 +1575,6 @@
       <c r="C88" t="n">
         <v>316.6763581</v>
       </c>
-      <c r="D88" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E88" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2120,12 +1588,6 @@
       <c r="C89" t="n">
         <v>319.0018219</v>
       </c>
-      <c r="D89" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E89" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2139,12 +1601,6 @@
       <c r="C90" t="n">
         <v>321.5765314</v>
       </c>
-      <c r="D90" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E90" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2158,12 +1614,6 @@
       <c r="C91" t="n">
         <v>323.9581049</v>
       </c>
-      <c r="D91" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E91" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2177,12 +1627,6 @@
       <c r="C92" t="n">
         <v>326.2651329</v>
       </c>
-      <c r="D92" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E92" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2196,12 +1640,6 @@
       <c r="C93" t="n">
         <v>328.0157885</v>
       </c>
-      <c r="D93" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E93" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2215,12 +1653,6 @@
       <c r="C94" t="n">
         <v>330.0725424</v>
       </c>
-      <c r="D94" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E94" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2234,12 +1666,6 @@
       <c r="C95" t="n">
         <v>332.0479022</v>
       </c>
-      <c r="D95" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E95" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2253,12 +1679,6 @@
       <c r="C96" t="n">
         <v>333.9363797</v>
       </c>
-      <c r="D96" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E96" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2272,12 +1692,6 @@
       <c r="C97" t="n">
         <v>335.6189001</v>
       </c>
-      <c r="D97" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E97" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2291,12 +1705,6 @@
       <c r="C98" t="n">
         <v>337.2625786</v>
       </c>
-      <c r="D98" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E98" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2310,12 +1718,6 @@
       <c r="C99" t="n">
         <v>338.7650399</v>
       </c>
-      <c r="D99" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E99" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2329,12 +1731,6 @@
       <c r="C100" t="n">
         <v>340.2361363000001</v>
       </c>
-      <c r="D100" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E100" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2348,12 +1744,6 @@
       <c r="C101" t="n">
         <v>341.7250045</v>
       </c>
-      <c r="D101" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E101" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2367,12 +1757,6 @@
       <c r="C102" t="n">
         <v>343.1774111</v>
       </c>
-      <c r="D102" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E102" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2386,12 +1770,6 @@
       <c r="C103" t="n">
         <v>344.2575904</v>
       </c>
-      <c r="D103" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E103" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2405,12 +1783,6 @@
       <c r="C104" t="n">
         <v>345.4963246</v>
       </c>
-      <c r="D104" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E104" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2424,12 +1796,6 @@
       <c r="C105" t="n">
         <v>346.5239814</v>
       </c>
-      <c r="D105" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E105" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2443,12 +1809,6 @@
       <c r="C106" t="n">
         <v>347.6881545</v>
       </c>
-      <c r="D106" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E106" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2462,12 +1822,6 @@
       <c r="C107" t="n">
         <v>348.774064</v>
       </c>
-      <c r="D107" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E107" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2481,12 +1835,6 @@
       <c r="C108" t="n">
         <v>349.5950335</v>
       </c>
-      <c r="D108" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E108" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2500,12 +1848,6 @@
       <c r="C109" t="n">
         <v>350.2011671</v>
       </c>
-      <c r="D109" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E109" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2519,12 +1861,6 @@
       <c r="C110" t="n">
         <v>350.8596784</v>
       </c>
-      <c r="D110" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E110" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2538,12 +1874,6 @@
       <c r="C111" t="n">
         <v>351.7060778</v>
       </c>
-      <c r="D111" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E111" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2557,12 +1887,6 @@
       <c r="C112" t="n">
         <v>352.7293787</v>
       </c>
-      <c r="D112" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E112" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2576,12 +1900,6 @@
       <c r="C113" t="n">
         <v>353.7333028</v>
       </c>
-      <c r="D113" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E113" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2595,12 +1913,6 @@
       <c r="C114" t="n">
         <v>354.5253749</v>
       </c>
-      <c r="D114" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E114" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2614,12 +1926,6 @@
       <c r="C115" t="n">
         <v>355.3300937</v>
       </c>
-      <c r="D115" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E115" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2633,12 +1939,6 @@
       <c r="C116" t="n">
         <v>355.9975024</v>
       </c>
-      <c r="D116" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E116" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2652,12 +1952,6 @@
       <c r="C117" t="n">
         <v>356.7722324</v>
       </c>
-      <c r="D117" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E117" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2671,12 +1965,6 @@
       <c r="C118" t="n">
         <v>357.4820016</v>
       </c>
-      <c r="D118" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E118" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2690,12 +1978,6 @@
       <c r="C119" t="n">
         <v>358.241956</v>
       </c>
-      <c r="D119" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E119" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2709,12 +1991,6 @@
       <c r="C120" t="n">
         <v>358.9015649</v>
       </c>
-      <c r="D120" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E120" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2728,12 +2004,6 @@
       <c r="C121" t="n">
         <v>359.6783189</v>
       </c>
-      <c r="D121" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E121" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2747,12 +2017,6 @@
       <c r="C122" t="n">
         <v>360.3704777</v>
       </c>
-      <c r="D122" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E122" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2766,12 +2030,6 @@
       <c r="C123" t="n">
         <v>361.0733082</v>
       </c>
-      <c r="D123" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E123" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2785,12 +2043,6 @@
       <c r="C124" t="n">
         <v>361.5993118</v>
       </c>
-      <c r="D124" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E124" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2804,12 +2056,6 @@
       <c r="C125" t="n">
         <v>362.1235937</v>
       </c>
-      <c r="D125" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E125" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2823,12 +2069,6 @@
       <c r="C126" t="n">
         <v>362.5245348</v>
       </c>
-      <c r="D126" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E126" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2842,12 +2082,6 @@
       <c r="C127" t="n">
         <v>362.9438705</v>
       </c>
-      <c r="D127" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E127" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2861,12 +2095,6 @@
       <c r="C128" t="n">
         <v>363.2808388</v>
       </c>
-      <c r="D128" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E128" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2880,12 +2108,6 @@
       <c r="C129" t="n">
         <v>363.6867111</v>
       </c>
-      <c r="D129" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E129" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2899,12 +2121,6 @@
       <c r="C130" t="n">
         <v>364.0124532</v>
       </c>
-      <c r="D130" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E130" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2918,12 +2134,6 @@
       <c r="C131" t="n">
         <v>364.3612668</v>
       </c>
-      <c r="D131" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E131" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2937,12 +2147,6 @@
       <c r="C132" t="n">
         <v>364.5484768</v>
       </c>
-      <c r="D132" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E132" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2956,12 +2160,6 @@
       <c r="C133" t="n">
         <v>364.6166737</v>
       </c>
-      <c r="D133" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E133" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2975,12 +2173,6 @@
       <c r="C134" t="n">
         <v>364.9572317</v>
       </c>
-      <c r="D134" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E134" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2994,12 +2186,6 @@
       <c r="C135" t="n">
         <v>364.9794204</v>
       </c>
-      <c r="D135" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E135" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3013,12 +2199,6 @@
       <c r="C136" t="n">
         <v>365.082711</v>
       </c>
-      <c r="D136" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E136" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3032,12 +2212,6 @@
       <c r="C137" t="n">
         <v>365.2395359</v>
       </c>
-      <c r="D137" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E137" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3051,12 +2225,6 @@
       <c r="C138" t="n">
         <v>365.3835711</v>
       </c>
-      <c r="D138" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E138" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3070,12 +2238,6 @@
       <c r="C139" t="n">
         <v>365.4732799</v>
       </c>
-      <c r="D139" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E139" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3089,12 +2251,6 @@
       <c r="C140" t="n">
         <v>365.5429049</v>
       </c>
-      <c r="D140" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E140" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3108,12 +2264,6 @@
       <c r="C141" t="n">
         <v>365.5309769</v>
       </c>
-      <c r="D141" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E141" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3127,12 +2277,6 @@
       <c r="C142" t="n">
         <v>365.6019509</v>
       </c>
-      <c r="D142" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E142" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3146,12 +2290,6 @@
       <c r="C143" t="n">
         <v>365.5888244</v>
       </c>
-      <c r="D143" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E143" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3165,12 +2303,6 @@
       <c r="C144" t="n">
         <v>365.6563669</v>
       </c>
-      <c r="D144" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E144" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3184,12 +2316,6 @@
       <c r="C145" t="n">
         <v>365.5862491</v>
       </c>
-      <c r="D145" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E145" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3203,12 +2329,6 @@
       <c r="C146" t="n">
         <v>365.6009125</v>
       </c>
-      <c r="D146" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E146" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3222,12 +2342,6 @@
       <c r="C147" t="n">
         <v>365.4990767</v>
       </c>
-      <c r="D147" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E147" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3241,12 +2355,6 @@
       <c r="C148" t="n">
         <v>365.5073025</v>
       </c>
-      <c r="D148" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E148" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3260,12 +2368,6 @@
       <c r="C149" t="n">
         <v>365.4006924</v>
       </c>
-      <c r="D149" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E149" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3279,12 +2381,6 @@
       <c r="C150" t="n">
         <v>365.3988799</v>
       </c>
-      <c r="D150" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E150" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3298,12 +2394,6 @@
       <c r="C151" t="n">
         <v>365.2725027</v>
       </c>
-      <c r="D151" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E151" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3317,12 +2407,6 @@
       <c r="C152" t="n">
         <v>365.251968</v>
       </c>
-      <c r="D152" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E152" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3336,12 +2420,6 @@
       <c r="C153" t="n">
         <v>365.1151366</v>
       </c>
-      <c r="D153" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E153" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3355,12 +2433,6 @@
       <c r="C154" t="n">
         <v>365.0920791</v>
       </c>
-      <c r="D154" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E154" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3374,12 +2446,6 @@
       <c r="C155" t="n">
         <v>364.9556089</v>
       </c>
-      <c r="D155" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E155" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3393,12 +2459,6 @@
       <c r="C156" t="n">
         <v>364.9248112</v>
       </c>
-      <c r="D156" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E156" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3412,12 +2472,6 @@
       <c r="C157" t="n">
         <v>364.7699205</v>
       </c>
-      <c r="D157" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E157" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3431,12 +2485,6 @@
       <c r="C158" t="n">
         <v>364.7164411</v>
       </c>
-      <c r="D158" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E158" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3450,12 +2498,6 @@
       <c r="C159" t="n">
         <v>364.5536956</v>
       </c>
-      <c r="D159" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E159" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3469,12 +2511,6 @@
       <c r="C160" t="n">
         <v>364.4991033</v>
       </c>
-      <c r="D160" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E160" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3488,12 +2524,6 @@
       <c r="C161" t="n">
         <v>364.3321315</v>
       </c>
-      <c r="D161" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E161" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3507,12 +2537,6 @@
       <c r="C162" t="n">
         <v>364.2557828</v>
       </c>
-      <c r="D162" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E162" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3526,12 +2550,6 @@
       <c r="C163" t="n">
         <v>364.0650348</v>
       </c>
-      <c r="D163" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E163" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3545,12 +2563,6 @@
       <c r="C164" t="n">
         <v>363.968418</v>
       </c>
-      <c r="D164" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E164" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3564,12 +2576,6 @@
       <c r="C165" t="n">
         <v>363.7688522</v>
       </c>
-      <c r="D165" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E165" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3583,12 +2589,6 @@
       <c r="C166" t="n">
         <v>363.6648301</v>
       </c>
-      <c r="D166" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E166" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3602,12 +2602,6 @@
       <c r="C167" t="n">
         <v>363.4569753</v>
       </c>
-      <c r="D167" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E167" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3621,12 +2615,6 @@
       <c r="C168" t="n">
         <v>363.3364455</v>
       </c>
-      <c r="D168" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E168" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3640,12 +2628,6 @@
       <c r="C169" t="n">
         <v>363.1104895</v>
       </c>
-      <c r="D169" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E169" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3659,12 +2641,6 @@
       <c r="C170" t="n">
         <v>362.9704464</v>
       </c>
-      <c r="D170" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E170" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3678,12 +2654,6 @@
       <c r="C171" t="n">
         <v>362.7294574</v>
       </c>
-      <c r="D171" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E171" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3697,12 +2667,6 @@
       <c r="C172" t="n">
         <v>362.57516</v>
       </c>
-      <c r="D172" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E172" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3716,12 +2680,6 @@
       <c r="C173" t="n">
         <v>362.3257481</v>
       </c>
-      <c r="D173" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E173" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3735,12 +2693,6 @@
       <c r="C174" t="n">
         <v>362.1630316</v>
       </c>
-      <c r="D174" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E174" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3754,12 +2706,6 @@
       <c r="C175" t="n">
         <v>361.904625</v>
       </c>
-      <c r="D175" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E175" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3773,12 +2719,6 @@
       <c r="C176" t="n">
         <v>361.7246336</v>
       </c>
-      <c r="D176" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E176" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3792,12 +2732,6 @@
       <c r="C177" t="n">
         <v>361.4507333</v>
       </c>
-      <c r="D177" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E177" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3811,12 +2745,6 @@
       <c r="C178" t="n">
         <v>361.2619233</v>
       </c>
-      <c r="D178" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E178" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3830,12 +2758,6 @@
       <c r="C179" t="n">
         <v>360.9918766</v>
       </c>
-      <c r="D179" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E179" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3849,12 +2771,6 @@
       <c r="C180" t="n">
         <v>360.8066985</v>
       </c>
-      <c r="D180" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E180" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3868,12 +2784,6 @@
       <c r="C181" t="n">
         <v>360.5405574</v>
       </c>
-      <c r="D181" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E181" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3887,12 +2797,6 @@
       <c r="C182" t="n">
         <v>360.3461475</v>
       </c>
-      <c r="D182" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E182" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3906,12 +2810,6 @@
       <c r="C183" t="n">
         <v>360.0628412</v>
       </c>
-      <c r="D183" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E183" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3925,12 +2823,6 @@
       <c r="C184" t="n">
         <v>359.8436556</v>
       </c>
-      <c r="D184" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E184" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3944,12 +2836,6 @@
       <c r="C185" t="n">
         <v>359.5364106</v>
       </c>
-      <c r="D185" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E185" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3963,12 +2849,6 @@
       <c r="C186" t="n">
         <v>359.290422</v>
       </c>
-      <c r="D186" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E186" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3982,12 +2862,6 @@
       <c r="C187" t="n">
         <v>358.9512588</v>
       </c>
-      <c r="D187" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E187" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4001,12 +2875,6 @@
       <c r="C188" t="n">
         <v>358.6664998</v>
       </c>
-      <c r="D188" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E188" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4020,12 +2888,6 @@
       <c r="C189" t="n">
         <v>358.2847901</v>
       </c>
-      <c r="D189" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E189" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4039,12 +2901,6 @@
       <c r="C190" t="n">
         <v>357.9495757</v>
       </c>
-      <c r="D190" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E190" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4058,12 +2914,6 @@
       <c r="C191" t="n">
         <v>357.5089055</v>
       </c>
-      <c r="D191" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E191" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4077,12 +2927,6 @@
       <c r="C192" t="n">
         <v>357.1143353</v>
       </c>
-      <c r="D192" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E192" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4096,12 +2940,6 @@
       <c r="C193" t="n">
         <v>356.6172923</v>
       </c>
-      <c r="D193" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E193" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4115,12 +2953,6 @@
       <c r="C194" t="n">
         <v>356.1680397</v>
       </c>
-      <c r="D194" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E194" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4134,12 +2966,6 @@
       <c r="C195" t="n">
         <v>355.6168646</v>
       </c>
-      <c r="D195" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E195" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4153,12 +2979,6 @@
       <c r="C196" t="n">
         <v>355.1183956</v>
       </c>
-      <c r="D196" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E196" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4172,12 +2992,6 @@
       <c r="C197" t="n">
         <v>354.5230181</v>
       </c>
-      <c r="D197" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E197" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4191,12 +3005,6 @@
       <c r="C198" t="n">
         <v>353.9787723</v>
       </c>
-      <c r="D198" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E198" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4210,12 +3018,6 @@
       <c r="C199" t="n">
         <v>353.3365571</v>
       </c>
-      <c r="D199" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E199" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4229,12 +3031,6 @@
       <c r="C200" t="n">
         <v>352.7394465</v>
       </c>
-      <c r="D200" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E200" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4248,12 +3044,6 @@
       <c r="C201" t="n">
         <v>352.0410998</v>
       </c>
-      <c r="D201" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E201" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4267,12 +3057,6 @@
       <c r="C202" t="n">
         <v>351.3686573</v>
       </c>
-      <c r="D202" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E202" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4286,12 +3070,6 @@
       <c r="C203" t="n">
         <v>350.5848606</v>
       </c>
-      <c r="D203" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E203" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4305,12 +3083,6 @@
       <c r="C204" t="n">
         <v>349.8205201</v>
       </c>
-      <c r="D204" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E204" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4324,12 +3096,6 @@
       <c r="C205" t="n">
         <v>348.9609819</v>
       </c>
-      <c r="D205" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E205" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4343,12 +3109,6 @@
       <c r="C206" t="n">
         <v>348.1427736</v>
       </c>
-      <c r="D206" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E206" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4362,12 +3122,6 @@
       <c r="C207" t="n">
         <v>347.2137974</v>
       </c>
-      <c r="D207" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E207" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4381,12 +3135,6 @@
       <c r="C208" t="n">
         <v>346.2496641</v>
       </c>
-      <c r="D208" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E208" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4400,12 +3148,6 @@
       <c r="C209" t="n">
         <v>345.150223</v>
       </c>
-      <c r="D209" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E209" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4419,12 +3161,6 @@
       <c r="C210" t="n">
         <v>344.058968</v>
       </c>
-      <c r="D210" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E210" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4438,12 +3174,6 @@
       <c r="C211" t="n">
         <v>342.9439897</v>
       </c>
-      <c r="D211" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E211" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4457,12 +3187,6 @@
       <c r="C212" t="n">
         <v>341.81940581</v>
       </c>
-      <c r="D212" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E212" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4476,12 +3200,6 @@
       <c r="C213" t="n">
         <v>340.54093154</v>
       </c>
-      <c r="D213" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E213" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4495,12 +3213,6 @@
       <c r="C214" t="n">
         <v>339.21707189</v>
       </c>
-      <c r="D214" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E214" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4514,12 +3226,6 @@
       <c r="C215" t="n">
         <v>337.80525138</v>
       </c>
-      <c r="D215" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E215" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4533,12 +3239,6 @@
       <c r="C216" t="n">
         <v>336.43396568</v>
       </c>
-      <c r="D216" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E216" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4552,12 +3252,6 @@
       <c r="C217" t="n">
         <v>335.003024</v>
       </c>
-      <c r="D217" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E217" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4571,12 +3265,6 @@
       <c r="C218" t="n">
         <v>333.58656266</v>
       </c>
-      <c r="D218" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E218" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4590,12 +3278,6 @@
       <c r="C219" t="n">
         <v>332.10205328</v>
       </c>
-      <c r="D219" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E219" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4609,12 +3291,6 @@
       <c r="C220" t="n">
         <v>330.64761558</v>
       </c>
-      <c r="D220" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E220" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4628,12 +3304,6 @@
       <c r="C221" t="n">
         <v>329.165471146</v>
       </c>
-      <c r="D221" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E221" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4647,12 +3317,6 @@
       <c r="C222" t="n">
         <v>327.752144285</v>
       </c>
-      <c r="D222" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E222" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4666,12 +3330,6 @@
       <c r="C223" t="n">
         <v>326.35106964</v>
       </c>
-      <c r="D223" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E223" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4685,12 +3343,6 @@
       <c r="C224" t="n">
         <v>325.01809444</v>
       </c>
-      <c r="D224" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E224" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4704,12 +3356,6 @@
       <c r="C225" t="n">
         <v>323.67382696</v>
       </c>
-      <c r="D225" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E225" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4723,12 +3369,6 @@
       <c r="C226" t="n">
         <v>322.38934004</v>
       </c>
-      <c r="D226" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E226" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4742,12 +3382,6 @@
       <c r="C227" t="n">
         <v>321.10680423</v>
       </c>
-      <c r="D227" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E227" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4761,12 +3395,6 @@
       <c r="C228" t="n">
         <v>319.88479103</v>
       </c>
-      <c r="D228" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E228" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4780,12 +3408,6 @@
       <c r="C229" t="n">
         <v>318.65108842</v>
       </c>
-      <c r="D229" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E229" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4799,12 +3421,6 @@
       <c r="C230" t="n">
         <v>317.4456847</v>
       </c>
-      <c r="D230" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E230" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4818,12 +3434,6 @@
       <c r="C231" t="n">
         <v>316.18783914</v>
       </c>
-      <c r="D231" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E231" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4837,12 +3447,6 @@
       <c r="C232" t="n">
         <v>314.9082049</v>
       </c>
-      <c r="D232" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E232" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4856,12 +3460,6 @@
       <c r="C233" t="n">
         <v>313.5626117</v>
       </c>
-      <c r="D233" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E233" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4875,12 +3473,6 @@
       <c r="C234" t="n">
         <v>312.1504419</v>
       </c>
-      <c r="D234" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E234" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4894,12 +3486,6 @@
       <c r="C235" t="n">
         <v>310.5947018</v>
       </c>
-      <c r="D235" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E235" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4913,12 +3499,6 @@
       <c r="C236" t="n">
         <v>308.8955139</v>
       </c>
-      <c r="D236" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E236" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4932,12 +3512,6 @@
       <c r="C237" t="n">
         <v>307.1540847</v>
       </c>
-      <c r="D237" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E237" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4951,12 +3525,6 @@
       <c r="C238" t="n">
         <v>305.4174554</v>
       </c>
-      <c r="D238" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E238" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4970,12 +3538,6 @@
       <c r="C239" t="n">
         <v>303.3886367</v>
       </c>
-      <c r="D239" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E239" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4989,12 +3551,6 @@
       <c r="C240" t="n">
         <v>301.3396008</v>
       </c>
-      <c r="D240" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E240" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -5008,12 +3564,6 @@
       <c r="C241" t="n">
         <v>299.3294777</v>
       </c>
-      <c r="D241" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E241" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5027,12 +3577,6 @@
       <c r="C242" t="n">
         <v>297.2809485</v>
       </c>
-      <c r="D242" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E242" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5046,12 +3590,6 @@
       <c r="C243" t="n">
         <v>295.1692119</v>
       </c>
-      <c r="D243" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E243" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5065,12 +3603,6 @@
       <c r="C244" t="n">
         <v>293.0981086</v>
       </c>
-      <c r="D244" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E244" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5084,12 +3616,6 @@
       <c r="C245" t="n">
         <v>291.0809054</v>
       </c>
-      <c r="D245" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E245" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5103,12 +3629,6 @@
       <c r="C246" t="n">
         <v>289.16972</v>
       </c>
-      <c r="D246" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E246" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5122,12 +3642,6 @@
       <c r="C247" t="n">
         <v>287.3323711</v>
       </c>
-      <c r="D247" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E247" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -5141,12 +3655,6 @@
       <c r="C248" t="n">
         <v>285.6012672</v>
       </c>
-      <c r="D248" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E248" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -5160,12 +3668,6 @@
       <c r="C249" t="n">
         <v>283.9501975</v>
       </c>
-      <c r="D249" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E249" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -5179,12 +3681,6 @@
       <c r="C250" t="n">
         <v>282.4294889</v>
       </c>
-      <c r="D250" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E250" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -5198,12 +3694,6 @@
       <c r="C251" t="n">
         <v>281.0020604</v>
       </c>
-      <c r="D251" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E251" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -5217,12 +3707,6 @@
       <c r="C252" t="n">
         <v>279.6991666</v>
       </c>
-      <c r="D252" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E252" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -5236,12 +3720,6 @@
       <c r="C253" t="n">
         <v>278.4732061</v>
       </c>
-      <c r="D253" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E253" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5255,12 +3733,6 @@
       <c r="C254" t="n">
         <v>277.3472708</v>
       </c>
-      <c r="D254" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E254" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5274,12 +3746,6 @@
       <c r="C255" t="n">
         <v>276.2598388</v>
       </c>
-      <c r="D255" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E255" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5293,12 +3759,6 @@
       <c r="C256" t="n">
         <v>275.2425592</v>
       </c>
-      <c r="D256" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E256" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5312,12 +3772,6 @@
       <c r="C257" t="n">
         <v>274.2553086</v>
       </c>
-      <c r="D257" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E257" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5331,12 +3785,6 @@
       <c r="C258" t="n">
         <v>273.3512832</v>
       </c>
-      <c r="D258" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E258" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5350,12 +3798,6 @@
       <c r="C259" t="n">
         <v>272.4748194</v>
       </c>
-      <c r="D259" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E259" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5369,12 +3811,6 @@
       <c r="C260" t="n">
         <v>271.6760132</v>
       </c>
-      <c r="D260" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E260" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5388,12 +3824,6 @@
       <c r="C261" t="n">
         <v>270.9130798</v>
       </c>
-      <c r="D261" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E261" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5407,12 +3837,6 @@
       <c r="C262" t="n">
         <v>270.2325585</v>
       </c>
-      <c r="D262" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E262" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5426,12 +3850,6 @@
       <c r="C263" t="n">
         <v>269.5792544</v>
       </c>
-      <c r="D263" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E263" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5445,12 +3863,6 @@
       <c r="C264" t="n">
         <v>268.9982721</v>
       </c>
-      <c r="D264" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E264" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5464,12 +3876,6 @@
       <c r="C265" t="n">
         <v>268.4541756</v>
       </c>
-      <c r="D265" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E265" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5483,12 +3889,6 @@
       <c r="C266" t="n">
         <v>267.9904429</v>
       </c>
-      <c r="D266" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E266" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -5502,12 +3902,6 @@
       <c r="C267" t="n">
         <v>267.5520597</v>
       </c>
-      <c r="D267" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E267" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -5521,12 +3915,6 @@
       <c r="C268" t="n">
         <v>267.1728749</v>
       </c>
-      <c r="D268" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E268" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5540,12 +3928,6 @@
       <c r="C269" t="n">
         <v>266.80304</v>
       </c>
-      <c r="D269" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E269" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5559,12 +3941,6 @@
       <c r="C270" t="n">
         <v>266.4814025</v>
       </c>
-      <c r="D270" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E270" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5578,12 +3954,6 @@
       <c r="C271" t="n">
         <v>266.1570328</v>
       </c>
-      <c r="D271" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E271" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5597,12 +3967,6 @@
       <c r="C272" t="n">
         <v>265.8712241</v>
       </c>
-      <c r="D272" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E272" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5616,12 +3980,6 @@
       <c r="C273" t="n">
         <v>265.5667901</v>
       </c>
-      <c r="D273" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E273" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5635,12 +3993,6 @@
       <c r="C274" t="n">
         <v>265.2836537</v>
       </c>
-      <c r="D274" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E274" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5654,12 +4006,6 @@
       <c r="C275" t="n">
         <v>264.9702091</v>
       </c>
-      <c r="D275" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E275" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5673,12 +4019,6 @@
       <c r="C276" t="n">
         <v>264.6753903</v>
       </c>
-      <c r="D276" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E276" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5692,12 +4032,6 @@
       <c r="C277" t="n">
         <v>264.3465614</v>
       </c>
-      <c r="D277" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E277" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5711,12 +4045,6 @@
       <c r="C278" t="n">
         <v>264.0400621</v>
       </c>
-      <c r="D278" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E278" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5730,12 +4058,6 @@
       <c r="C279" t="n">
         <v>263.7061156</v>
       </c>
-      <c r="D279" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E279" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5749,12 +4071,6 @@
       <c r="C280" t="n">
         <v>263.3947111</v>
       </c>
-      <c r="D280" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E280" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5768,12 +4084,6 @@
       <c r="C281" t="n">
         <v>263.0600815</v>
       </c>
-      <c r="D281" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E281" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5787,12 +4097,6 @@
       <c r="C282" t="n">
         <v>262.753446</v>
       </c>
-      <c r="D282" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E282" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5806,12 +4110,6 @@
       <c r="C283" t="n">
         <v>262.4284674</v>
       </c>
-      <c r="D283" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E283" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5825,12 +4123,6 @@
       <c r="C284" t="n">
         <v>262.1311535</v>
       </c>
-      <c r="D284" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E284" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5844,12 +4136,6 @@
       <c r="C285" t="n">
         <v>261.8176413</v>
       </c>
-      <c r="D285" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E285" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5863,12 +4149,6 @@
       <c r="C286" t="n">
         <v>261.52621</v>
       </c>
-      <c r="D286" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E286" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5882,12 +4162,6 @@
       <c r="C287" t="n">
         <v>261.2063789</v>
       </c>
-      <c r="D287" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E287" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5901,12 +4175,6 @@
       <c r="C288" t="n">
         <v>260.898109</v>
       </c>
-      <c r="D288" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E288" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5920,12 +4188,6 @@
       <c r="C289" t="n">
         <v>260.5699173</v>
       </c>
-      <c r="D289" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E289" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5939,12 +4201,6 @@
       <c r="C290" t="n">
         <v>260.2363887</v>
       </c>
-      <c r="D290" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E290" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5958,12 +4214,6 @@
       <c r="C291" t="n">
         <v>259.8466118</v>
       </c>
-      <c r="D291" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E291" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5977,12 +4227,6 @@
       <c r="C292" t="n">
         <v>259.4417116</v>
       </c>
-      <c r="D292" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E292" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5996,12 +4240,6 @@
       <c r="C293" t="n">
         <v>259.0185887</v>
       </c>
-      <c r="D293" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E293" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -6015,12 +4253,6 @@
       <c r="C294" t="n">
         <v>258.5179867</v>
       </c>
-      <c r="D294" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E294" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -6034,12 +4266,6 @@
       <c r="C295" t="n">
         <v>257.9411503</v>
       </c>
-      <c r="D295" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E295" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -6053,12 +4279,6 @@
       <c r="C296" t="n">
         <v>257.3239722</v>
       </c>
-      <c r="D296" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E296" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -6072,12 +4292,6 @@
       <c r="C297" t="n">
         <v>256.7199445</v>
       </c>
-      <c r="D297" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E297" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -6091,12 +4305,6 @@
       <c r="C298" t="n">
         <v>256.0963515</v>
       </c>
-      <c r="D298" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E298" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -6110,12 +4318,6 @@
       <c r="C299" t="n">
         <v>255.505177</v>
       </c>
-      <c r="D299" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E299" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -6129,12 +4331,6 @@
       <c r="C300" t="n">
         <v>254.8335035</v>
       </c>
-      <c r="D300" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E300" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -6148,12 +4344,6 @@
       <c r="C301" t="n">
         <v>254.2238742</v>
       </c>
-      <c r="D301" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E301" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -6167,12 +4357,6 @@
       <c r="C302" t="n">
         <v>253.5089361</v>
       </c>
-      <c r="D302" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E302" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -6186,12 +4370,6 @@
       <c r="C303" t="n">
         <v>253.2358533</v>
       </c>
-      <c r="D303" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E303" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -6205,12 +4383,6 @@
       <c r="C304" t="n">
         <v>252.556198</v>
       </c>
-      <c r="D304" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E304" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -6224,12 +4396,6 @@
       <c r="C305" t="n">
         <v>252.9999049</v>
       </c>
-      <c r="D305" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E305" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -6243,12 +4409,6 @@
       <c r="C306" t="n">
         <v>252.1198871</v>
       </c>
-      <c r="D306" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E306" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -6262,12 +4422,6 @@
       <c r="C307" t="n">
         <v>253.7006595</v>
       </c>
-      <c r="D307" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E307" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -6281,12 +4435,6 @@
       <c r="C308" t="n">
         <v>252.1908836</v>
       </c>
-      <c r="D308" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E308" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -6300,12 +4448,6 @@
       <c r="C309" t="n">
         <v>250.9014693</v>
       </c>
-      <c r="D309" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E309" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6319,12 +4461,6 @@
       <c r="C310" t="n">
         <v>249.1939481</v>
       </c>
-      <c r="D310" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E310" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6338,12 +4474,6 @@
       <c r="C311" t="n">
         <v>248.7447145</v>
       </c>
-      <c r="D311" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E311" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6357,12 +4487,6 @@
       <c r="C312" t="n">
         <v>248.7155809</v>
       </c>
-      <c r="D312" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E312" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6376,12 +4500,6 @@
       <c r="C313" t="n">
         <v>248.8699845</v>
       </c>
-      <c r="D313" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E313" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6395,12 +4513,6 @@
       <c r="C314" t="n">
         <v>248.8836348</v>
       </c>
-      <c r="D314" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E314" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6414,12 +4526,6 @@
       <c r="C315" t="n">
         <v>248.6490039</v>
       </c>
-      <c r="D315" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E315" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6433,12 +4539,6 @@
       <c r="C316" t="n">
         <v>248.2755447</v>
       </c>
-      <c r="D316" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E316" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6452,12 +4552,6 @@
       <c r="C317" t="n">
         <v>247.9623479</v>
       </c>
-      <c r="D317" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E317" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6471,12 +4565,6 @@
       <c r="C318" t="n">
         <v>247.8671492</v>
       </c>
-      <c r="D318" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E318" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6490,12 +4578,6 @@
       <c r="C319" t="n">
         <v>248.0064079</v>
       </c>
-      <c r="D319" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E319" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6509,12 +4591,6 @@
       <c r="C320" t="n">
         <v>248.1917181</v>
       </c>
-      <c r="D320" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E320" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6528,12 +4604,6 @@
       <c r="C321" t="n">
         <v>248.2310533</v>
       </c>
-      <c r="D321" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E321" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6547,12 +4617,6 @@
       <c r="C322" t="n">
         <v>248.2003837</v>
       </c>
-      <c r="D322" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E322" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6566,12 +4630,6 @@
       <c r="C323" t="n">
         <v>248.1111815</v>
       </c>
-      <c r="D323" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E323" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6585,12 +4643,6 @@
       <c r="C324" t="n">
         <v>248.1087348</v>
       </c>
-      <c r="D324" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E324" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6604,12 +4656,6 @@
       <c r="C325" t="n">
         <v>248.1168452</v>
       </c>
-      <c r="D325" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E325" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6623,12 +4669,6 @@
       <c r="C326" t="n">
         <v>248.1846065</v>
       </c>
-      <c r="D326" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E326" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6642,12 +4682,6 @@
       <c r="C327" t="n">
         <v>248.2413851</v>
       </c>
-      <c r="D327" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E327" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6661,12 +4695,6 @@
       <c r="C328" t="n">
         <v>248.3223484</v>
       </c>
-      <c r="D328" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E328" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6680,12 +4708,6 @@
       <c r="C329" t="n">
         <v>248.3354061</v>
       </c>
-      <c r="D329" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E329" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6699,12 +4721,6 @@
       <c r="C330" t="n">
         <v>248.4001244</v>
       </c>
-      <c r="D330" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E330" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6718,12 +4734,6 @@
       <c r="C331" t="n">
         <v>248.4238542</v>
       </c>
-      <c r="D331" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E331" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -6737,12 +4747,6 @@
       <c r="C332" t="n">
         <v>248.4621558</v>
       </c>
-      <c r="D332" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E332" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6756,12 +4760,6 @@
       <c r="C333" t="n">
         <v>248.5702455</v>
       </c>
-      <c r="D333" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E333" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6775,12 +4773,6 @@
       <c r="C334" t="n">
         <v>248.6857884</v>
       </c>
-      <c r="D334" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E334" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6794,12 +4786,6 @@
       <c r="C335" t="n">
         <v>248.8695699</v>
       </c>
-      <c r="D335" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E335" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6813,12 +4799,6 @@
       <c r="C336" t="n">
         <v>249.0313278</v>
       </c>
-      <c r="D336" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E336" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6832,12 +4812,6 @@
       <c r="C337" t="n">
         <v>249.2170733</v>
       </c>
-      <c r="D337" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E337" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6851,12 +4825,6 @@
       <c r="C338" t="n">
         <v>249.3987661</v>
       </c>
-      <c r="D338" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E338" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6870,12 +4838,6 @@
       <c r="C339" t="n">
         <v>249.5699427</v>
       </c>
-      <c r="D339" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E339" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6889,12 +4851,6 @@
       <c r="C340" t="n">
         <v>249.7164449</v>
       </c>
-      <c r="D340" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E340" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6908,12 +4864,6 @@
       <c r="C341" t="n">
         <v>249.8705061</v>
       </c>
-      <c r="D341" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E341" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6927,12 +4877,6 @@
       <c r="C342" t="n">
         <v>249.9954143</v>
       </c>
-      <c r="D342" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E342" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -6946,12 +4890,6 @@
       <c r="C343" t="n">
         <v>250.1305448</v>
       </c>
-      <c r="D343" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E343" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -6965,12 +4903,6 @@
       <c r="C344" t="n">
         <v>250.2264154</v>
       </c>
-      <c r="D344" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E344" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -6984,12 +4916,6 @@
       <c r="C345" t="n">
         <v>250.3354205</v>
       </c>
-      <c r="D345" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E345" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -7003,12 +4929,6 @@
       <c r="C346" t="n">
         <v>250.3901823</v>
       </c>
-      <c r="D346" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E346" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -7022,12 +4942,6 @@
       <c r="C347" t="n">
         <v>250.4551281</v>
       </c>
-      <c r="D347" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E347" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -7041,12 +4955,6 @@
       <c r="C348" t="n">
         <v>250.4688469</v>
       </c>
-      <c r="D348" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E348" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -7060,12 +4968,6 @@
       <c r="C349" t="n">
         <v>250.5083893</v>
       </c>
-      <c r="D349" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E349" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -7079,12 +4981,6 @@
       <c r="C350" t="n">
         <v>250.5043593</v>
       </c>
-      <c r="D350" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E350" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -7098,12 +4994,6 @@
       <c r="C351" t="n">
         <v>250.5278081</v>
       </c>
-      <c r="D351" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E351" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -7117,12 +5007,6 @@
       <c r="C352" t="n">
         <v>250.5047676</v>
       </c>
-      <c r="D352" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E352" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -7136,12 +5020,6 @@
       <c r="C353" t="n">
         <v>250.5030706</v>
       </c>
-      <c r="D353" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E353" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -7155,12 +5033,6 @@
       <c r="C354" t="n">
         <v>250.4567719</v>
       </c>
-      <c r="D354" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E354" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -7174,12 +5046,6 @@
       <c r="C355" t="n">
         <v>250.4320709</v>
       </c>
-      <c r="D355" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E355" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -7193,12 +5059,6 @@
       <c r="C356" t="n">
         <v>250.3433272</v>
       </c>
-      <c r="D356" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E356" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -7212,12 +5072,6 @@
       <c r="C357" t="n">
         <v>250.3062631</v>
       </c>
-      <c r="D357" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E357" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -7231,12 +5085,6 @@
       <c r="C358" t="n">
         <v>250.2171383</v>
       </c>
-      <c r="D358" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E358" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -7250,12 +5098,6 @@
       <c r="C359" t="n">
         <v>250.1687414</v>
       </c>
-      <c r="D359" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E359" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -7269,12 +5111,6 @@
       <c r="C360" t="n">
         <v>250.0732595</v>
       </c>
-      <c r="D360" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E360" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -7288,12 +5124,6 @@
       <c r="C361" t="n">
         <v>250.0201786</v>
       </c>
-      <c r="D361" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E361" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -7307,12 +5137,6 @@
       <c r="C362" t="n">
         <v>249.9088208</v>
       </c>
-      <c r="D362" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E362" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -7326,12 +5150,6 @@
       <c r="C363" t="n">
         <v>249.8235277</v>
       </c>
-      <c r="D363" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E363" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -7345,12 +5163,6 @@
       <c r="C364" t="n">
         <v>249.6809359</v>
       </c>
-      <c r="D364" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E364" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -7364,12 +5176,6 @@
       <c r="C365" t="n">
         <v>249.5757345</v>
       </c>
-      <c r="D365" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E365" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -7383,12 +5189,6 @@
       <c r="C366" t="n">
         <v>249.4121941</v>
       </c>
-      <c r="D366" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E366" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -7402,12 +5202,6 @@
       <c r="C367" t="n">
         <v>249.2888349</v>
       </c>
-      <c r="D367" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E367" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -7421,12 +5215,6 @@
       <c r="C368" t="n">
         <v>249.1073197</v>
       </c>
-      <c r="D368" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E368" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -7440,12 +5228,6 @@
       <c r="C369" t="n">
         <v>248.9713609</v>
       </c>
-      <c r="D369" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E369" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -7459,12 +5241,6 @@
       <c r="C370" t="n">
         <v>248.7738179</v>
       </c>
-      <c r="D370" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E370" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -7478,12 +5254,6 @@
       <c r="C371" t="n">
         <v>248.6275729</v>
       </c>
-      <c r="D371" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E371" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -7497,12 +5267,6 @@
       <c r="C372" t="n">
         <v>248.4245233</v>
       </c>
-      <c r="D372" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E372" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -7516,12 +5280,6 @@
       <c r="C373" t="n">
         <v>248.2842637</v>
       </c>
-      <c r="D373" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E373" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -7535,12 +5293,6 @@
       <c r="C374" t="n">
         <v>248.0847031</v>
       </c>
-      <c r="D374" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E374" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -7554,12 +5306,6 @@
       <c r="C375" t="n">
         <v>247.9499953</v>
       </c>
-      <c r="D375" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E375" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -7573,12 +5319,6 @@
       <c r="C376" t="n">
         <v>247.7560867</v>
       </c>
-      <c r="D376" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E376" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -7592,12 +5332,6 @@
       <c r="C377" t="n">
         <v>247.6339788</v>
       </c>
-      <c r="D377" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E377" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -7611,12 +5345,6 @@
       <c r="C378" t="n">
         <v>247.4588144</v>
       </c>
-      <c r="D378" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E378" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -7630,12 +5358,6 @@
       <c r="C379" t="n">
         <v>247.3636067</v>
       </c>
-      <c r="D379" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E379" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -7649,12 +5371,6 @@
       <c r="C380" t="n">
         <v>247.2085236</v>
       </c>
-      <c r="D380" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E380" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -7668,12 +5384,6 @@
       <c r="C381" t="n">
         <v>247.1358643</v>
       </c>
-      <c r="D381" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E381" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -7687,12 +5397,6 @@
       <c r="C382" t="n">
         <v>247.0000389</v>
       </c>
-      <c r="D382" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E382" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -7706,12 +5410,6 @@
       <c r="C383" t="n">
         <v>246.9519077</v>
       </c>
-      <c r="D383" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E383" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -7725,12 +5423,6 @@
       <c r="C384" t="n">
         <v>246.8958036</v>
       </c>
-      <c r="D384" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E384" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -7744,12 +5436,6 @@
       <c r="C385" t="n">
         <v>246.8497985</v>
       </c>
-      <c r="D385" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E385" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -7763,12 +5449,6 @@
       <c r="C386" t="n">
         <v>246.7555632</v>
       </c>
-      <c r="D386" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E386" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -7782,12 +5462,6 @@
       <c r="C387" t="n">
         <v>246.712816</v>
       </c>
-      <c r="D387" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E387" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -7801,12 +5475,6 @@
       <c r="C388" t="n">
         <v>246.6627563</v>
       </c>
-      <c r="D388" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E388" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -7820,12 +5488,6 @@
       <c r="C389" t="n">
         <v>246.6528116</v>
       </c>
-      <c r="D389" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E389" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -7839,12 +5501,6 @@
       <c r="C390" t="n">
         <v>246.6337437</v>
       </c>
-      <c r="D390" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E390" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -7858,12 +5514,6 @@
       <c r="C391" t="n">
         <v>246.6884781</v>
       </c>
-      <c r="D391" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E391" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -7877,12 +5527,6 @@
       <c r="C392" t="n">
         <v>246.6660438</v>
       </c>
-      <c r="D392" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E392" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -7896,12 +5540,6 @@
       <c r="C393" t="n">
         <v>246.6951892</v>
       </c>
-      <c r="D393" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E393" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -7915,12 +5553,6 @@
       <c r="C394" t="n">
         <v>246.6921927</v>
       </c>
-      <c r="D394" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E394" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -7934,12 +5566,6 @@
       <c r="C395" t="n">
         <v>246.760576</v>
       </c>
-      <c r="D395" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E395" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -7953,12 +5579,6 @@
       <c r="C396" t="n">
         <v>246.7836007</v>
       </c>
-      <c r="D396" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E396" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -7972,12 +5592,6 @@
       <c r="C397" t="n">
         <v>246.8628703</v>
       </c>
-      <c r="D397" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E397" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -7991,12 +5605,6 @@
       <c r="C398" t="n">
         <v>246.9000426</v>
       </c>
-      <c r="D398" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E398" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -8010,12 +5618,6 @@
       <c r="C399" t="n">
         <v>247.0230454</v>
       </c>
-      <c r="D399" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E399" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -8029,12 +5631,6 @@
       <c r="C400" t="n">
         <v>247.4161636</v>
       </c>
-      <c r="D400" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E400" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -8048,12 +5644,6 @@
       <c r="C401" t="n">
         <v>247.7217431</v>
       </c>
-      <c r="D401" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E401" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -8067,12 +5657,6 @@
       <c r="C402" t="n">
         <v>247.5428002</v>
       </c>
-      <c r="D402" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E402" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -8086,12 +5670,6 @@
       <c r="C403" t="n">
         <v>247.4922634</v>
       </c>
-      <c r="D403" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E403" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -8105,12 +5683,6 @@
       <c r="C404" t="n">
         <v>247.5043695</v>
       </c>
-      <c r="D404" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E404" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -8124,12 +5696,6 @@
       <c r="C405" t="n">
         <v>247.7056084</v>
       </c>
-      <c r="D405" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E405" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -8143,12 +5709,6 @@
       <c r="C406" t="n">
         <v>248.2541542</v>
       </c>
-      <c r="D406" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E406" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -8162,12 +5722,6 @@
       <c r="C407" t="n">
         <v>248.5670586</v>
       </c>
-      <c r="D407" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E407" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -8181,12 +5735,6 @@
       <c r="C408" t="n">
         <v>248.2739511</v>
       </c>
-      <c r="D408" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E408" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -8200,12 +5748,6 @@
       <c r="C409" t="n">
         <v>248.0503443</v>
       </c>
-      <c r="D409" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E409" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -8219,12 +5761,6 @@
       <c r="C410" t="n">
         <v>248.3631459</v>
       </c>
-      <c r="D410" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E410" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -8238,12 +5774,6 @@
       <c r="C411" t="n">
         <v>248.7568687</v>
       </c>
-      <c r="D411" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E411" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -8257,12 +5787,6 @@
       <c r="C412" t="n">
         <v>248.6168212</v>
       </c>
-      <c r="D412" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E412" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -8276,12 +5800,6 @@
       <c r="C413" t="n">
         <v>248.435088</v>
       </c>
-      <c r="D413" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E413" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -8295,12 +5813,6 @@
       <c r="C414" t="n">
         <v>248.6708873</v>
       </c>
-      <c r="D414" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E414" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -8314,12 +5826,6 @@
       <c r="C415" t="n">
         <v>248.9278504</v>
       </c>
-      <c r="D415" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E415" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -8333,12 +5839,6 @@
       <c r="C416" t="n">
         <v>248.6703101</v>
       </c>
-      <c r="D416" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E416" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -8352,12 +5852,6 @@
       <c r="C417" t="n">
         <v>248.4226595</v>
       </c>
-      <c r="D417" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E417" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -8371,12 +5865,6 @@
       <c r="C418" t="n">
         <v>248.7010964</v>
       </c>
-      <c r="D418" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E418" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -8390,12 +5878,6 @@
       <c r="C419" t="n">
         <v>249.0228614</v>
       </c>
-      <c r="D419" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E419" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -8409,12 +5891,6 @@
       <c r="C420" t="n">
         <v>248.7742626</v>
       </c>
-      <c r="D420" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E420" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -8428,12 +5904,6 @@
       <c r="C421" t="n">
         <v>248.4984026</v>
       </c>
-      <c r="D421" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E421" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -8447,12 +5917,6 @@
       <c r="C422" t="n">
         <v>248.7443906</v>
       </c>
-      <c r="D422" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E422" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -8466,12 +5930,6 @@
       <c r="C423" t="n">
         <v>249.0633796</v>
       </c>
-      <c r="D423" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E423" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -8485,12 +5943,6 @@
       <c r="C424" t="n">
         <v>248.7975112</v>
       </c>
-      <c r="D424" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E424" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -8504,12 +5956,6 @@
       <c r="C425" t="n">
         <v>248.5635363</v>
       </c>
-      <c r="D425" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E425" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -8523,12 +5969,6 @@
       <c r="C426" t="n">
         <v>248.9151119</v>
       </c>
-      <c r="D426" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E426" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -8542,12 +5982,6 @@
       <c r="C427" t="n">
         <v>249.2823076</v>
       </c>
-      <c r="D427" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E427" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -8561,12 +5995,6 @@
       <c r="C428" t="n">
         <v>248.9875679</v>
       </c>
-      <c r="D428" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E428" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -8580,12 +6008,6 @@
       <c r="C429" t="n">
         <v>248.7468334</v>
       </c>
-      <c r="D429" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E429" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -8599,12 +6021,6 @@
       <c r="C430" t="n">
         <v>249.1513843</v>
       </c>
-      <c r="D430" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E430" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -8618,12 +6034,6 @@
       <c r="C431" t="n">
         <v>249.5679041</v>
       </c>
-      <c r="D431" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E431" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -8637,12 +6047,6 @@
       <c r="C432" t="n">
         <v>249.3338786</v>
       </c>
-      <c r="D432" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E432" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -8656,12 +6060,6 @@
       <c r="C433" t="n">
         <v>249.096231</v>
       </c>
-      <c r="D433" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E433" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -8675,12 +6073,6 @@
       <c r="C434" t="n">
         <v>249.5180748</v>
       </c>
-      <c r="D434" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E434" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -8694,12 +6086,6 @@
       <c r="C435" t="n">
         <v>249.9237649</v>
       </c>
-      <c r="D435" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E435" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -8713,12 +6099,6 @@
       <c r="C436" t="n">
         <v>249.6701139</v>
       </c>
-      <c r="D436" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E436" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -8732,12 +6112,6 @@
       <c r="C437" t="n">
         <v>249.3993301</v>
       </c>
-      <c r="D437" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E437" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -8751,12 +6125,6 @@
       <c r="C438" t="n">
         <v>249.7955961</v>
       </c>
-      <c r="D438" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E438" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -8770,12 +6138,6 @@
       <c r="C439" t="n">
         <v>250.2440472</v>
       </c>
-      <c r="D439" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E439" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -8789,12 +6151,6 @@
       <c r="C440" t="n">
         <v>250.3290128</v>
       </c>
-      <c r="D440" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E440" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -8808,12 +6164,6 @@
       <c r="C441" t="n">
         <v>250.2168436</v>
       </c>
-      <c r="D441" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E441" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -8827,12 +6177,6 @@
       <c r="C442" t="n">
         <v>250.0605515</v>
       </c>
-      <c r="D442" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E442" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -8846,12 +6190,6 @@
       <c r="C443" t="n">
         <v>250.0107637</v>
       </c>
-      <c r="D443" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E443" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -8865,12 +6203,6 @@
       <c r="C444" t="n">
         <v>250.0366807</v>
       </c>
-      <c r="D444" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E444" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -8884,12 +6216,6 @@
       <c r="C445" t="n">
         <v>250.1128886</v>
       </c>
-      <c r="D445" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E445" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -8903,12 +6229,6 @@
       <c r="C446" t="n">
         <v>250.1410931</v>
       </c>
-      <c r="D446" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E446" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -8922,12 +6242,6 @@
       <c r="C447" t="n">
         <v>250.1455221</v>
       </c>
-      <c r="D447" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E447" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -8941,12 +6255,6 @@
       <c r="C448" t="n">
         <v>250.1055426</v>
       </c>
-      <c r="D448" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E448" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -8960,12 +6268,6 @@
       <c r="C449" t="n">
         <v>250.0716358</v>
       </c>
-      <c r="D449" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E449" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -8979,12 +6281,6 @@
       <c r="C450" t="n">
         <v>250.0016238</v>
       </c>
-      <c r="D450" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E450" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -8998,12 +6294,6 @@
       <c r="C451" t="n">
         <v>249.9428255</v>
       </c>
-      <c r="D451" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E451" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -9017,12 +6307,6 @@
       <c r="C452" t="n">
         <v>249.8497284</v>
       </c>
-      <c r="D452" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E452" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -9036,12 +6320,6 @@
       <c r="C453" t="n">
         <v>249.7547572</v>
       </c>
-      <c r="D453" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E453" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -9055,12 +6333,6 @@
       <c r="C454" t="n">
         <v>249.626021</v>
       </c>
-      <c r="D454" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E454" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -9074,12 +6346,6 @@
       <c r="C455" t="n">
         <v>249.5045212</v>
       </c>
-      <c r="D455" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E455" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -9093,12 +6359,6 @@
       <c r="C456" t="n">
         <v>249.3550843</v>
       </c>
-      <c r="D456" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E456" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -9112,12 +6372,6 @@
       <c r="C457" t="n">
         <v>249.2176563</v>
       </c>
-      <c r="D457" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E457" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -9131,12 +6385,6 @@
       <c r="C458" t="n">
         <v>249.0506409</v>
       </c>
-      <c r="D458" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E458" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -9150,12 +6398,6 @@
       <c r="C459" t="n">
         <v>248.9255311</v>
       </c>
-      <c r="D459" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E459" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -9169,12 +6411,6 @@
       <c r="C460" t="n">
         <v>248.7813717</v>
       </c>
-      <c r="D460" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E460" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -9188,12 +6424,6 @@
       <c r="C461" t="n">
         <v>248.6662461</v>
       </c>
-      <c r="D461" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E461" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -9207,12 +6437,6 @@
       <c r="C462" t="n">
         <v>248.5329212</v>
       </c>
-      <c r="D462" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E462" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -9226,12 +6450,6 @@
       <c r="C463" t="n">
         <v>248.4352192</v>
       </c>
-      <c r="D463" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E463" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -9245,12 +6463,6 @@
       <c r="C464" t="n">
         <v>248.3227034</v>
       </c>
-      <c r="D464" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E464" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -9264,12 +6476,6 @@
       <c r="C465" t="n">
         <v>248.2479811</v>
       </c>
-      <c r="D465" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E465" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -9283,12 +6489,6 @@
       <c r="C466" t="n">
         <v>248.1602091</v>
       </c>
-      <c r="D466" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E466" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -9302,12 +6502,6 @@
       <c r="C467" t="n">
         <v>248.1093027</v>
       </c>
-      <c r="D467" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E467" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -9321,12 +6515,6 @@
       <c r="C468" t="n">
         <v>248.0446143</v>
       </c>
-      <c r="D468" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E468" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -9340,12 +6528,6 @@
       <c r="C469" t="n">
         <v>248.0178004</v>
       </c>
-      <c r="D469" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E469" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -9359,12 +6541,6 @@
       <c r="C470" t="n">
         <v>247.9708999</v>
       </c>
-      <c r="D470" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E470" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -9378,12 +6554,6 @@
       <c r="C471" t="n">
         <v>247.9595591</v>
       </c>
-      <c r="D471" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E471" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -9397,12 +6567,6 @@
       <c r="C472" t="n">
         <v>247.9382829</v>
       </c>
-      <c r="D472" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E472" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -9416,12 +6580,6 @@
       <c r="C473" t="n">
         <v>247.9562461</v>
       </c>
-      <c r="D473" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E473" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -9435,12 +6593,6 @@
       <c r="C474" t="n">
         <v>247.9598238</v>
       </c>
-      <c r="D474" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E474" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -9454,12 +6606,6 @@
       <c r="C475" t="n">
         <v>247.9948822</v>
       </c>
-      <c r="D475" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E475" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -9473,12 +6619,6 @@
       <c r="C476" t="n">
         <v>248.0136644</v>
       </c>
-      <c r="D476" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E476" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -9492,12 +6632,6 @@
       <c r="C477" t="n">
         <v>248.06319</v>
       </c>
-      <c r="D477" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E477" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -9511,12 +6645,6 @@
       <c r="C478" t="n">
         <v>248.1038043</v>
       </c>
-      <c r="D478" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E478" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -9530,12 +6658,6 @@
       <c r="C479" t="n">
         <v>248.1703788</v>
       </c>
-      <c r="D479" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E479" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -9549,12 +6671,6 @@
       <c r="C480" t="n">
         <v>248.2315569</v>
       </c>
-      <c r="D480" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E480" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -9568,12 +6684,6 @@
       <c r="C481" t="n">
         <v>248.3105524</v>
       </c>
-      <c r="D481" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E481" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -9587,12 +6697,6 @@
       <c r="C482" t="n">
         <v>248.3859842</v>
       </c>
-      <c r="D482" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E482" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -9606,12 +6710,6 @@
       <c r="C483" t="n">
         <v>248.4679868</v>
       </c>
-      <c r="D483" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E483" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -9625,12 +6723,6 @@
       <c r="C484" t="n">
         <v>248.5559708</v>
       </c>
-      <c r="D484" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E484" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -9644,12 +6736,6 @@
       <c r="C485" t="n">
         <v>248.6447515</v>
       </c>
-      <c r="D485" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E485" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -9663,12 +6749,6 @@
       <c r="C486" t="n">
         <v>248.7477642</v>
       </c>
-      <c r="D486" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E486" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -9682,12 +6762,6 @@
       <c r="C487" t="n">
         <v>248.8423757</v>
       </c>
-      <c r="D487" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E487" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -9701,12 +6775,6 @@
       <c r="C488" t="n">
         <v>248.9609333</v>
       </c>
-      <c r="D488" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E488" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -9720,12 +6788,6 @@
       <c r="C489" t="n">
         <v>249.0586777</v>
       </c>
-      <c r="D489" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E489" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -9739,12 +6801,6 @@
       <c r="C490" t="n">
         <v>249.1832899</v>
       </c>
-      <c r="D490" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E490" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -9758,12 +6814,6 @@
       <c r="C491" t="n">
         <v>249.2796397</v>
       </c>
-      <c r="D491" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E491" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -9777,12 +6827,6 @@
       <c r="C492" t="n">
         <v>249.422607</v>
       </c>
-      <c r="D492" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E492" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -9796,12 +6840,6 @@
       <c r="C493" t="n">
         <v>249.5265319</v>
       </c>
-      <c r="D493" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E493" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -9815,12 +6853,6 @@
       <c r="C494" t="n">
         <v>249.6763239</v>
       </c>
-      <c r="D494" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E494" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -9834,12 +6866,6 @@
       <c r="C495" t="n">
         <v>249.7766397</v>
       </c>
-      <c r="D495" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E495" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -9853,12 +6879,6 @@
       <c r="C496" t="n">
         <v>249.9249004</v>
       </c>
-      <c r="D496" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E496" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -9872,12 +6892,6 @@
       <c r="C497" t="n">
         <v>250.0224883</v>
       </c>
-      <c r="D497" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E497" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -9891,12 +6905,6 @@
       <c r="C498" t="n">
         <v>250.1657985</v>
       </c>
-      <c r="D498" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E498" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -9910,12 +6918,6 @@
       <c r="C499" t="n">
         <v>250.2678334</v>
       </c>
-      <c r="D499" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E499" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -9929,12 +6931,6 @@
       <c r="C500" t="n">
         <v>250.4138967</v>
       </c>
-      <c r="D500" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E500" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -9948,12 +6944,6 @@
       <c r="C501" t="n">
         <v>250.5333539</v>
       </c>
-      <c r="D501" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E501" t="n">
-        <v>292.4819396333533</v>
-      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -9966,12 +6956,6 @@
       </c>
       <c r="C502" t="n">
         <v>250.6836378</v>
-      </c>
-      <c r="D502" t="n">
-        <v>1933.701022251497</v>
-      </c>
-      <c r="E502" t="n">
-        <v>292.4819396333533</v>
       </c>
     </row>
   </sheetData>
